--- a/results/Int Task Remove ACC -0.9/Rando_fi_explain.xlsx
+++ b/results/Int Task Remove ACC -0.9/Rando_fi_explain.xlsx
@@ -1148,268 +1148,268 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.001913882734821303</v>
+        <v>0.0007780073320758595</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.001359535652120233</v>
+        <v>-0.002845813683854149</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0001828382518498483</v>
+        <v>-0.000293009436837458</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001102117221562731</v>
+        <v>0.002018662942289677</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.0005770269842058841</v>
+        <v>-0.0004334120430794133</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0001913872617206726</v>
+        <v>-0.0007522060440710967</v>
       </c>
       <c r="I3" t="n">
-        <v>-4.004029677572295e-06</v>
+        <v>0.0001001006221559575</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.0007229828986689445</v>
+        <v>0.001925756857035647</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01526564748158607</v>
+        <v>0.01697487940156318</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01728421484605801</v>
+        <v>0.02023033299065658</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.002195967970045331</v>
+        <v>-0.0001846028617640629</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0008195529236561617</v>
+        <v>-0.001346649136611627</v>
       </c>
       <c r="O3" t="n">
-        <v>0.003059268576814524</v>
+        <v>0.003873454830901615</v>
       </c>
       <c r="P3" t="n">
-        <v>0.003246460841134902</v>
+        <v>0.003895905126430279</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.009156813357461024</v>
+        <v>0.01007276459008764</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.0004125896277679452</v>
+        <v>5.36381725052483e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.001708033832367157</v>
+        <v>-0.001251022269338083</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0003812284245238896</v>
+        <v>-0.0013806994541648</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.001945062322141879</v>
+        <v>-0.001115024374949516</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.0001250327962687514</v>
+        <v>0.0002289153739038019</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0007854469099923914</v>
+        <v>0.0004371637685860938</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.002977402584886771</v>
+        <v>-0.0007876737806804009</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.001508307518141079</v>
+        <v>0.0019221061753492</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.001897288135278081</v>
+        <v>0.0009478824825056032</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.002348084341900448</v>
+        <v>0.002646130263103526</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0005639381720194082</v>
+        <v>0.0002160918062363404</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.004394502724882491</v>
+        <v>0.005639508647716076</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0.002695775713593047</v>
+        <v>-0.00296149914559904</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0.002640734361312191</v>
+        <v>-0.002067198935220068</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.001517073835636707</v>
+        <v>-0.0002030696128360132</v>
       </c>
       <c r="AG3" t="n">
-        <v>-2.614024018052889e-05</v>
+        <v>-0.0003621875831386745</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.0003301832316732455</v>
+        <v>-2.482583839322652e-05</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-0.003523663551272733</v>
+        <v>-0.001266286558777924</v>
       </c>
       <c r="AK3" t="n">
-        <v>-0.000418019182718944</v>
+        <v>-0.004240430946722422</v>
       </c>
       <c r="AL3" t="n">
-        <v>-0.0002205867644291692</v>
+        <v>-4.503325351712052e-05</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.0001186766922751581</v>
+        <v>-0.0002664187706916121</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.001521164182056276</v>
+        <v>0.00106978275820571</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0.003315707675971823</v>
+        <v>-0.003062259410318006</v>
       </c>
       <c r="AP3" t="n">
-        <v>-0.0005110612311146413</v>
+        <v>-0.0001184403547418522</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.001230929612106391</v>
+        <v>0.0005863009323809542</v>
       </c>
       <c r="AR3" t="n">
-        <v>-0.00227453881961254</v>
+        <v>-0.001247960504498682</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.0006186417281047495</v>
+        <v>0.001547000888925242</v>
       </c>
       <c r="AT3" t="n">
-        <v>-0.003020655679628428</v>
+        <v>-0.004852729305451031</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.162267103409394e-05</v>
+        <v>0.002614600801515697</v>
       </c>
       <c r="AV3" t="n">
-        <v>-2.037460915100824e-05</v>
+        <v>0.0007004437742266168</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.0002694671149125692</v>
+        <v>0.001005423654985754</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.0002108644932246894</v>
+        <v>-0.0001559322629661275</v>
       </c>
       <c r="AY3" t="n">
-        <v>-0.001624515914650568</v>
+        <v>0.002586082062934085</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.004413015597294838</v>
+        <v>0.0001098209210502488</v>
       </c>
       <c r="BA3" t="n">
-        <v>-0.003037083942208951</v>
+        <v>-0.003357444643571642</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.000662532919332569</v>
+        <v>-0.002893959946577545</v>
       </c>
       <c r="BC3" t="n">
-        <v>-0.0001523929716596861</v>
+        <v>-0.0002063222590861202</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.797222220137896e-05</v>
+        <v>3.789391938169188e-05</v>
       </c>
       <c r="BE3" t="n">
-        <v>-6.801884178095949e-06</v>
+        <v>-0.0002076948339643381</v>
       </c>
       <c r="BF3" t="n">
-        <v>-0.003642595370567342</v>
+        <v>-0.004656548652647491</v>
       </c>
       <c r="BG3" t="n">
-        <v>-0.000200397200753456</v>
+        <v>0.0007157220813295473</v>
       </c>
       <c r="BH3" t="n">
-        <v>-1.480165778567244e-05</v>
+        <v>0</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.000288064602016449</v>
+        <v>0.0003949791797050949</v>
       </c>
       <c r="BJ3" t="n">
-        <v>-0.001100569843131793</v>
+        <v>0.0005893652040620423</v>
       </c>
       <c r="BK3" t="n">
-        <v>-0.001276070465489343</v>
+        <v>-0.001701657251052958</v>
       </c>
       <c r="BL3" t="n">
-        <v>-0.000234332728979778</v>
+        <v>0.0001699216736126941</v>
       </c>
       <c r="BM3" t="n">
-        <v>-0.0007013802117346867</v>
+        <v>-0.0006594068926119646</v>
       </c>
       <c r="BN3" t="n">
-        <v>-0.002687659057649264</v>
+        <v>-0.003846212548637467</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.0002346551943941921</v>
+        <v>0.001437156754804579</v>
       </c>
       <c r="BP3" t="n">
-        <v>-0.0001718713369383785</v>
+        <v>0.001516863508440176</v>
       </c>
       <c r="BQ3" t="n">
-        <v>-8.226025230604229e-05</v>
+        <v>8.749005395177764e-06</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.0004921529348590769</v>
+        <v>0.0004010026360289097</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.0004155554350052215</v>
+        <v>0.0002621491320197889</v>
       </c>
       <c r="BT3" t="n">
-        <v>-0.0002217023609654955</v>
+        <v>-0.0003932824568671811</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.00532335374730303</v>
+        <v>0.002990539108116518</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.0002530719432434957</v>
+        <v>-0.0005384269162258691</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.0002294183676163772</v>
+        <v>0.0001834226610493019</v>
       </c>
       <c r="BX3" t="n">
-        <v>-3.256856913960162e-06</v>
+        <v>4.969550943669242e-05</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.0001390388355217242</v>
+        <v>-0.0008108382048720019</v>
       </c>
       <c r="BZ3" t="n">
-        <v>-0.0007400352361339503</v>
+        <v>0.0006557299587656995</v>
       </c>
       <c r="CA3" t="n">
-        <v>6.611524758547428e-06</v>
+        <v>-1.189767995240843e-05</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.0001403933246108202</v>
+        <v>0.0001647261297206071</v>
       </c>
       <c r="CC3" t="n">
-        <v>-5.238644401124775e-05</v>
+        <v>0.001323961438850809</v>
       </c>
       <c r="CD3" t="n">
-        <v>-0.0002652275671226423</v>
+        <v>-0.0002355419305927797</v>
       </c>
       <c r="CE3" t="n">
-        <v>0.0003805609739314019</v>
+        <v>-0.0004052303511179201</v>
       </c>
       <c r="CF3" t="n">
-        <v>0.0009375421510965777</v>
+        <v>-0.0006822707204793778</v>
       </c>
       <c r="CG3" t="n">
-        <v>0.0002285893188731292</v>
+        <v>0.001037959596573163</v>
       </c>
       <c r="CH3" t="n">
-        <v>-0.0005878410585402838</v>
+        <v>0.000124789188717841</v>
       </c>
       <c r="CI3" t="n">
-        <v>-0.0009782761427259499</v>
+        <v>0.001617174328862463</v>
       </c>
       <c r="CJ3" t="n">
-        <v>-0.0001380174050850193</v>
+        <v>0.003368648151517586</v>
       </c>
       <c r="CK3" t="n">
-        <v>-0.0002588297604621515</v>
+        <v>-0.0006233931287187389</v>
       </c>
     </row>
     <row r="4">
@@ -1419,268 +1419,268 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.003233314588198098</v>
+        <v>0.002797404440851589</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0.007325462689159328</v>
+        <v>0.005816274441408307</v>
       </c>
       <c r="E4" t="n">
-        <v>0.007443447085653971</v>
+        <v>0.007002084244862847</v>
       </c>
       <c r="F4" t="n">
-        <v>0.002039051805127231</v>
+        <v>0.003547487010792501</v>
       </c>
       <c r="G4" t="n">
-        <v>0.005167344673911898</v>
+        <v>0.007911097467922063</v>
       </c>
       <c r="H4" t="n">
-        <v>0.005584090673533947</v>
+        <v>0.004755144100847423</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0002968607655970255</v>
+        <v>0.0002988528773645499</v>
       </c>
       <c r="J4" t="n">
-        <v>0.005808242925589653</v>
+        <v>0.006707694391747138</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01563300379418481</v>
+        <v>0.01511289834006379</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01331368069721429</v>
+        <v>0.01439504311075462</v>
       </c>
       <c r="M4" t="n">
-        <v>0.004383841889717488</v>
+        <v>0.004702460206982109</v>
       </c>
       <c r="N4" t="n">
-        <v>0.005091516418451625</v>
+        <v>0.007601888962110776</v>
       </c>
       <c r="O4" t="n">
-        <v>0.006405566896010356</v>
+        <v>0.008857380165020296</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01035804426428072</v>
+        <v>0.0127470016536731</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.008932002010120142</v>
+        <v>0.01086328890911165</v>
       </c>
       <c r="R4" t="n">
-        <v>0.004857290765399016</v>
+        <v>0.003980740059631532</v>
       </c>
       <c r="S4" t="n">
-        <v>0.005277577495253245</v>
+        <v>0.002889250227510965</v>
       </c>
       <c r="T4" t="n">
-        <v>0.002969143005581149</v>
+        <v>0.004793583767738125</v>
       </c>
       <c r="U4" t="n">
-        <v>0.005216323692888769</v>
+        <v>0.003613282971355209</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0002038160574445373</v>
+        <v>0.0002407259771119269</v>
       </c>
       <c r="W4" t="n">
-        <v>0.006324500408010075</v>
+        <v>0.008899352516167799</v>
       </c>
       <c r="X4" t="n">
-        <v>0.00405530187564692</v>
+        <v>0.004528180346145844</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.003748634182896918</v>
+        <v>0.001841142507120573</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.002716551917227889</v>
+        <v>0.003347362388295507</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.003028831196565129</v>
+        <v>0.004600669102820275</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0005995192577884141</v>
+        <v>0.0007074384985738395</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.006977259301000485</v>
+        <v>0.005070385360055335</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.00792611156624849</v>
+        <v>0.008335093287373292</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.004706688980811597</v>
+        <v>0.00274639303108815</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.004259115193572732</v>
+        <v>0.004707550674763931</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.0007970399709850991</v>
+        <v>0.0008640642526621667</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.0008802521075950981</v>
+        <v>0.0007309971683223943</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.004550194057292095</v>
+        <v>0.004290503147679381</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.00663940578276415</v>
+        <v>0.00694830056664466</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.0007653683239804212</v>
+        <v>0.0009112180102574366</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.001647141643894445</v>
+        <v>0.0009338909845803278</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.002910459684089981</v>
+        <v>0.005388647966055982</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.004682828635366304</v>
+        <v>0.004393816045324656</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.0009809576737827865</v>
+        <v>0.0008761362194118584</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.002522440102713433</v>
+        <v>0.001758012918460508</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.004710100655032269</v>
+        <v>0.004149840189033006</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.003789206219996797</v>
+        <v>0.002864143145444691</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.003389166261071635</v>
+        <v>0.009078982630372916</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.004156901191567958</v>
+        <v>0.006793258056156477</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.002238649389799065</v>
+        <v>0.00337344688822478</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.00327860951755602</v>
+        <v>0.005613140937269135</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.0005954696471457231</v>
+        <v>0.000639534594202636</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.003287160084098853</v>
+        <v>0.003073903347805944</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.006484234944587075</v>
+        <v>0.007739122670272973</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.007344777574004688</v>
+        <v>0.008038449970510442</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.005866275302153591</v>
+        <v>0.006718998301115969</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.0009106476214241307</v>
+        <v>0.001078643965766565</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.0007723264043666552</v>
+        <v>0.001475052522506937</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.001328426364348368</v>
+        <v>0.0007059488548100191</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.00576042251662443</v>
+        <v>0.01004314157823933</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.004786082184045411</v>
+        <v>0.008215381919445441</v>
       </c>
       <c r="BH4" t="n">
-        <v>4.680695174908931e-05</v>
+        <v>0</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.0006463197186046244</v>
+        <v>0.00122934211691602</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.002850442287599399</v>
+        <v>0.003589617518058957</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.003494239512816671</v>
+        <v>0.005398976824992971</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.00137272342326125</v>
+        <v>0.001007887530902703</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.003029662418808085</v>
+        <v>0.002920423071258934</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.007545081057495137</v>
+        <v>0.006051268881466349</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.002760102680255309</v>
+        <v>0.003244416345838331</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.003051554452771034</v>
+        <v>0.005740642228554461</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.0002281885510258028</v>
+        <v>0.0003428529703143703</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.003997158498026989</v>
+        <v>0.0049921097357154</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.002572079930086379</v>
+        <v>0.003401711403411797</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.001601534448506802</v>
+        <v>0.0009619453565152086</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.01064338572849862</v>
+        <v>0.007965254485192148</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.003239985397395835</v>
+        <v>0.002623771389029317</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.006368731278114392</v>
+        <v>0.006256030390455706</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.000117124769930603</v>
+        <v>0.0002359190819702561</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.001293056948796002</v>
+        <v>0.001691141417643127</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.001301141552484402</v>
+        <v>0.002410453356023907</v>
       </c>
       <c r="CA4" t="n">
-        <v>8.172113066277065e-05</v>
+        <v>3.762376752133435e-05</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.0008214566013535424</v>
+        <v>0.001475341859290193</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.003911640146859978</v>
+        <v>0.003560207672704152</v>
       </c>
       <c r="CD4" t="n">
-        <v>0.0008597214007743364</v>
+        <v>0.0008329576590043524</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.0006558023695953596</v>
+        <v>0.0007772615274129987</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.003125658093419343</v>
+        <v>0.002803345281486676</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.002817626659868384</v>
+        <v>0.004090350443472468</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.002087369110604208</v>
+        <v>0.00125455545203622</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.001849090346729043</v>
+        <v>0.007085958977055718</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.003157160095850572</v>
+        <v>0.006314696040947749</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.00248353197757614</v>
+        <v>0.002504896301705536</v>
       </c>
     </row>
     <row r="5">
@@ -1690,268 +1690,268 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.007073098549866874</v>
+        <v>-0.002989050014797246</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.01642497780408409</v>
+        <v>-0.0151228174015981</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.008210890233362123</v>
+        <v>-0.01109190435033136</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.00272269902337976</v>
+        <v>-0.005563776265167209</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.00849899164505904</v>
+        <v>-0.01347685048658217</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.006988404888749611</v>
+        <v>-0.009334485738980158</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0003256364712847848</v>
+        <v>-0.000503107428233196</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.01071322876590712</v>
+        <v>-0.004498372299496889</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.007375396139441071</v>
+        <v>-0.005002960331557171</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0003760576621748446</v>
+        <v>-0.002736963411120763</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.008923556942277745</v>
+        <v>-0.008525754884547099</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.006540396567031703</v>
+        <v>-0.01501008354940944</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.004492979719188828</v>
+        <v>-0.009363295880149836</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.009219245174301316</v>
+        <v>-0.0160118168389956</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.004806841639634329</v>
+        <v>-0.008758478324977902</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.009381473808819218</v>
+        <v>-0.007428233205090251</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.006511091904350308</v>
+        <v>-0.005045440300846149</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.004410894020130218</v>
+        <v>-0.01255180580224988</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.007858197932053135</v>
+        <v>-0.009363295880149836</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.000444049733570151</v>
+        <v>-0.0001480165778567577</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.006549670949545616</v>
+        <v>-0.009254347185381618</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.007610024449877728</v>
+        <v>-0.006204156479217582</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.004278728606356951</v>
+        <v>-0.0009766203018644394</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.002658924205378943</v>
+        <v>-0.00440958863569102</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.002567237163814151</v>
+        <v>-0.003847292098253896</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.0003256364712847737</v>
+        <v>-0.0008030933967876242</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.006155667357206329</v>
+        <v>-0.0007778738115816863</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.01927175843694491</v>
+        <v>-0.01829484902309061</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.008893643031784826</v>
+        <v>-0.00834813499111905</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.01132238547968882</v>
+        <v>-0.009053376585078177</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.001435257410296476</v>
+        <v>-0.00174607872151521</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.0008863080684596402</v>
+        <v>-0.001450133175495683</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0.01031403053874961</v>
+        <v>-0.007490415806546758</v>
       </c>
       <c r="AK5" t="n">
-        <v>-0.0126702190645352</v>
+        <v>-0.01785079928952047</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.001238836070296734</v>
+        <v>-0.001361349511689824</v>
       </c>
       <c r="AM5" t="n">
-        <v>-0.003271441202475711</v>
+        <v>-0.001746595618709323</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.002121684867394746</v>
+        <v>-0.004992614475627754</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.01163410301953817</v>
+        <v>-0.01142687981053879</v>
       </c>
       <c r="AP5" t="n">
-        <v>-0.002333825701624803</v>
+        <v>-0.001953240603728879</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.004105296145408976</v>
+        <v>-0.003137022787807009</v>
       </c>
       <c r="AR5" t="n">
-        <v>-0.007675507020280858</v>
+        <v>-0.008792184724689178</v>
       </c>
       <c r="AS5" t="n">
-        <v>-0.00458851391355829</v>
+        <v>-0.003370786516853963</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0.007376561570493734</v>
+        <v>-0.02607317775857105</v>
       </c>
       <c r="AU5" t="n">
-        <v>-0.004648985959438445</v>
+        <v>-0.008020124297129306</v>
       </c>
       <c r="AV5" t="n">
-        <v>-0.003666562206204971</v>
+        <v>-0.005121373593842527</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0.007058484586574454</v>
+        <v>-0.007605877268798644</v>
       </c>
       <c r="AX5" t="n">
+        <v>-0.001620984379605028</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>-0.002099655280476342</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>-0.01091904350331321</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>-0.01858254105445118</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>-0.01672386895475824</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>-0.001963117192147546</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>-0.002693901716992342</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>-0.001684867394695832</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>-0.03059636992221264</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>-0.01918755401901472</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>-0.001242971293282014</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>-0.006458271896195844</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>-0.01265113535830142</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>-0.001243339253996478</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>-0.006423919478981688</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>-0.01433205544087291</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>-0.003551346552234358</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>-0.009431181844974901</v>
+      </c>
+      <c r="BQ5" t="n">
         <v>-0.0006782659982306316</v>
       </c>
-      <c r="AY5" t="n">
-        <v>-0.00742589703588149</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>-0.0045865834633386</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>-0.01641185647425902</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>-0.00861154446177852</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>-0.002131950446557152</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>-0.001154529307282404</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>-0.001848950172359787</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>-0.01060842433697354</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>-0.007404206280610759</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>-0.0001480165778567244</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>-0.0005185825410544021</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>-0.005327019828351609</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>-0.006333853354134211</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>-0.001894612196565992</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>-0.005646787669259556</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>-0.02051282051282049</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>-0.003788102989050057</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>-0.00381769754365201</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>-0.0003848431024274679</v>
-      </c>
       <c r="BR5" t="n">
-        <v>-0.005139454716389847</v>
+        <v>-0.007104795737122594</v>
       </c>
       <c r="BS5" t="n">
-        <v>-0.003331295843520743</v>
+        <v>-0.005387803433984617</v>
       </c>
       <c r="BT5" t="n">
-        <v>-0.002851770604826076</v>
+        <v>-0.001983422143280078</v>
       </c>
       <c r="BU5" t="n">
-        <v>-0.003988183161004411</v>
+        <v>-0.00490398818316099</v>
       </c>
       <c r="BV5" t="n">
-        <v>-0.004980842911877415</v>
+        <v>-0.005429017160686467</v>
       </c>
       <c r="BW5" t="n">
-        <v>-0.01159511125039174</v>
+        <v>-0.006737699780633033</v>
       </c>
       <c r="BX5" t="n">
-        <v>-0.0002750611246943313</v>
+        <v>-0.0003432137285491632</v>
       </c>
       <c r="BY5" t="n">
-        <v>-0.002036979003447193</v>
+        <v>-0.004795737122557753</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0.002304811293575326</v>
+        <v>-0.002160402485942548</v>
       </c>
       <c r="CA5" t="n">
-        <v>-0.0001784651992861264</v>
+        <v>-0.0001189767995240842</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0.001385204833480713</v>
+        <v>-0.001031535514294091</v>
       </c>
       <c r="CC5" t="n">
-        <v>-0.00482607333124413</v>
+        <v>-0.005711749038176961</v>
       </c>
       <c r="CD5" t="n">
-        <v>-0.002711464780430328</v>
+        <v>-0.002593575007368065</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.0006581009088060252</v>
+        <v>-0.001296456352636166</v>
       </c>
       <c r="CF5" t="n">
-        <v>-0.003545232273838583</v>
+        <v>-0.005069260241673978</v>
       </c>
       <c r="CG5" t="n">
-        <v>-0.00363522406769039</v>
+        <v>-0.006717963894643364</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0.005010315355142958</v>
+        <v>-0.0021899970405445</v>
       </c>
       <c r="CI5" t="n">
-        <v>-0.004003667481662576</v>
+        <v>-0.004629902683574216</v>
       </c>
       <c r="CJ5" t="n">
-        <v>-0.005264807270448158</v>
+        <v>-0.002156573116691274</v>
       </c>
       <c r="CK5" t="n">
-        <v>-0.004888749608273268</v>
+        <v>-0.005119857946137907</v>
       </c>
     </row>
     <row r="6">
@@ -1961,268 +1961,268 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.004063853740936693</v>
+        <v>-0.001521202366635355</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.00307280127558846</v>
+        <v>-0.006076725281417078</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.005673977891344178</v>
+        <v>-0.003975034706084027</v>
       </c>
       <c r="F6" t="n">
-        <v>-3.742714265899394e-05</v>
+        <v>0.0004380595586331943</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.001942715065715373</v>
+        <v>-0.003613435579059271</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.003239473370579948</v>
+        <v>-0.002909431023796019</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0002144994651959775</v>
+        <v>-6.520427437403108e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.004677869858311789</v>
+        <v>-0.00189571435480575</v>
       </c>
       <c r="K6" t="n">
-        <v>0.005253140676248677</v>
+        <v>0.006402045522285715</v>
       </c>
       <c r="L6" t="n">
-        <v>0.00703335692913013</v>
+        <v>0.01550107930771064</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.005308331177003998</v>
+        <v>-0.001493527438142397</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.004365683425628783</v>
+        <v>-0.003986615016637568</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0009112302951613748</v>
+        <v>-0.001945800350473795</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.006077597331452694</v>
+        <v>-0.005156362819463805</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.004283161726731979</v>
+        <v>0.003783848777048815</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.001822460590322755</v>
+        <v>-0.002455834659414157</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.005385339406167078</v>
+        <v>-0.003349338777844663</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.00170523580773449</v>
+        <v>-0.002935882952559457</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.005575240987167607</v>
+        <v>-0.002204375693622762</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.0002725324454532857</v>
+        <v>6.713042528954383e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.003825902742630052</v>
+        <v>-0.006083308119140374</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.006053138183378746</v>
+        <v>-0.004114418734784339</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.001182049877716471</v>
+        <v>0.001203278554275422</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.0003161842275195171</v>
+        <v>-0.0005392478221306146</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.0006357321242551505</v>
+        <v>-0.0004010098809862445</v>
       </c>
       <c r="AB6" t="n">
-        <v>7.257432016365695e-05</v>
+        <v>-0.000317903020868715</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.0009609172135084804</v>
+        <v>0.002486459100488942</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0.005325240491735392</v>
+        <v>-0.008534239617890805</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0.006204766296388162</v>
+        <v>-0.002973653622626904</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.00336716765633176</v>
+        <v>-0.00332659061247001</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.000473342388013942</v>
+        <v>-0.00100384335089217</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0.0002635514578633563</v>
+        <v>-0.0003815192150036228</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-0.007118895636021036</v>
+        <v>-0.004438669755148113</v>
       </c>
       <c r="AK6" t="n">
-        <v>-0.004782006823989693</v>
+        <v>-0.0068311100471462</v>
       </c>
       <c r="AL6" t="n">
-        <v>-0.0006836286041218109</v>
+        <v>-0.0004431102794873548</v>
       </c>
       <c r="AM6" t="n">
-        <v>-0.0001006655728838152</v>
+        <v>-0.0008605605592168164</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.0001699719747873529</v>
+        <v>-0.003007311401069665</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.005841018056735531</v>
+        <v>-0.003976189976694455</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.0009325092104808058</v>
+        <v>-0.0005247460470758302</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.0002141331311867001</v>
+        <v>-0.0001404056162246786</v>
       </c>
       <c r="AR6" t="n">
-        <v>-0.005500632997148001</v>
+        <v>-0.003969374158382213</v>
       </c>
       <c r="AS6" t="n">
-        <v>-0.002093093452784042</v>
+        <v>0.0001255412177264492</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0.006182380919439339</v>
+        <v>-0.00608020434467064</v>
       </c>
       <c r="AU6" t="n">
-        <v>-0.003009131090848946</v>
+        <v>-0.0004110404203024609</v>
       </c>
       <c r="AV6" t="n">
-        <v>-0.001070858874603628</v>
+        <v>-0.001018070583396397</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.0003246549289912831</v>
+        <v>-0.002090881436633796</v>
       </c>
       <c r="AX6" t="n">
-        <v>-0.0003454733307503732</v>
+        <v>-0.0004015123776389212</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.003501357669300337</v>
+        <v>-3.180185031589964e-06</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-0.0004748901194345817</v>
+        <v>-0.005513140486909102</v>
       </c>
       <c r="BA6" t="n">
-        <v>-0.005562715790179079</v>
+        <v>-0.002283671301144233</v>
       </c>
       <c r="BB6" t="n">
-        <v>-0.00271804136292888</v>
+        <v>-0.004903032137344943</v>
       </c>
       <c r="BC6" t="n">
-        <v>-0.0005914327942340619</v>
+        <v>-0.0006618539564939768</v>
       </c>
       <c r="BD6" t="n">
-        <v>-0.0003743121316906711</v>
+        <v>-0.00069984250886993</v>
       </c>
       <c r="BE6" t="n">
-        <v>-0.0004939502399818301</v>
+        <v>-0.000271118661152614</v>
       </c>
       <c r="BF6" t="n">
-        <v>-0.007619022305741083</v>
+        <v>-0.005252041779461925</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.002654231508199892</v>
+        <v>-0.001821204115896508</v>
       </c>
       <c r="BH6" t="n">
         <v>0</v>
       </c>
       <c r="BI6" t="n">
-        <v>-0.0002367608173003494</v>
+        <v>-0.0002383626727018112</v>
       </c>
       <c r="BJ6" t="n">
-        <v>-0.003776315097547736</v>
+        <v>-0.0008807769322963926</v>
       </c>
       <c r="BK6" t="n">
-        <v>-0.003119801954074139</v>
+        <v>-0.00465912910245099</v>
       </c>
       <c r="BL6" t="n">
-        <v>-0.001403066256191446</v>
+        <v>-0.0008437815080335614</v>
       </c>
       <c r="BM6" t="n">
-        <v>-0.002479076871409486</v>
+        <v>-0.00227755999063321</v>
       </c>
       <c r="BN6" t="n">
-        <v>-0.003967111862958666</v>
+        <v>-0.005451044085732657</v>
       </c>
       <c r="BO6" t="n">
-        <v>-0.001600376374605575</v>
+        <v>-0.0008534470746339561</v>
       </c>
       <c r="BP6" t="n">
-        <v>-0.001927402713349605</v>
+        <v>-0.001370849612180966</v>
       </c>
       <c r="BQ6" t="n">
-        <v>-0.0001721121118433644</v>
+        <v>-0.0001760059723132118</v>
       </c>
       <c r="BR6" t="n">
-        <v>-0.00227231141792652</v>
+        <v>-0.002213076341430434</v>
       </c>
       <c r="BS6" t="n">
-        <v>-0.001132106142910749</v>
+        <v>-0.001926011942678219</v>
       </c>
       <c r="BT6" t="n">
-        <v>-0.001151039503271911</v>
+        <v>-0.0008127486521800453</v>
       </c>
       <c r="BU6" t="n">
-        <v>-0.0008659459837873779</v>
+        <v>-0.002361149412059346</v>
       </c>
       <c r="BV6" t="n">
-        <v>-0.001504423196487747</v>
+        <v>-0.002111520224213908</v>
       </c>
       <c r="BW6" t="n">
-        <v>-0.001706889032947711</v>
+        <v>-0.003573713307088952</v>
       </c>
       <c r="BX6" t="n">
-        <v>-3.71892966105014e-05</v>
+        <v>-8.075717910742964e-05</v>
       </c>
       <c r="BY6" t="n">
-        <v>-0.0004575365329186593</v>
+        <v>-0.0008585155184303278</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-0.001692609220086294</v>
+        <v>-0.0009998311742455801</v>
       </c>
       <c r="CA6" t="n">
         <v>0</v>
       </c>
       <c r="CB6" t="n">
-        <v>-0.0004366439584744197</v>
+        <v>-0.0006180886555753357</v>
       </c>
       <c r="CC6" t="n">
-        <v>-0.003200703280956971</v>
+        <v>0.000423634529750605</v>
       </c>
       <c r="CD6" t="n">
         <v>0</v>
       </c>
       <c r="CE6" t="n">
-        <v>-1.473184513529346e-05</v>
+        <v>-0.0008103010161372271</v>
       </c>
       <c r="CF6" t="n">
-        <v>-0.001371055152990705</v>
+        <v>-0.001420022858543668</v>
       </c>
       <c r="CG6" t="n">
-        <v>-0.002127454175394913</v>
+        <v>-0.0004773613601584042</v>
       </c>
       <c r="CH6" t="n">
-        <v>-0.001671272408876098</v>
+        <v>-0.0003571540460346496</v>
       </c>
       <c r="CI6" t="n">
-        <v>-0.002281352834539457</v>
+        <v>-0.002131127864983021</v>
       </c>
       <c r="CJ6" t="n">
-        <v>-0.002268195296083253</v>
+        <v>-0.001338360827065871</v>
       </c>
       <c r="CK6" t="n">
-        <v>-0.001296788974159388</v>
+        <v>-0.00239699620360436</v>
       </c>
     </row>
     <row r="7">
@@ -2232,268 +2232,268 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.002246141974124078</v>
+        <v>0.0007415847689855704</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.001242084283306777</v>
+        <v>-0.00132893485220259</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0002931560608627093</v>
+        <v>-0.00121109597269361</v>
       </c>
       <c r="F7" t="n">
-        <v>0.001020334897892622</v>
+        <v>0.003498938450559097</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.0009941061049045462</v>
+        <v>-0.0007229017082930112</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.0009402115017418722</v>
+        <v>-0.001197320490666337</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.881014116966618e-05</v>
+        <v>0.0001624256187250039</v>
       </c>
       <c r="J7" t="n">
-        <v>0.000838155142248126</v>
+        <v>-0.0002204816087757744</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0131835826559991</v>
+        <v>0.01473896540945983</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01888864374640702</v>
+        <v>0.01959392208183147</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.0008552094606822547</v>
+        <v>-0.001038376070190361</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.001999735972936018</v>
+        <v>-4.237162063547295e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0006112050265706271</v>
+        <v>0.002574898012426368</v>
       </c>
       <c r="P7" t="n">
-        <v>0.002506600445363277</v>
+        <v>0.002975107516851178</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.007408232030879802</v>
+        <v>0.008835126616157929</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0001849828648969709</v>
+        <v>0.0008477882971466455</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.003801805254839591</v>
+        <v>-0.001741572421916215</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0008085824171519041</v>
+        <v>-0.001445866959539299</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.00332223232192227</v>
+        <v>-0.000657830591727826</v>
       </c>
       <c r="V7" t="n">
-        <v>-9.02353526853139e-05</v>
+        <v>0.0002887321107601814</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0001479727730097413</v>
+        <v>-0.001023705748790632</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.003074102067927586</v>
+        <v>-0.00135681941667703</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.002245258827551172</v>
+        <v>0.001592079957417836</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.00250543324465134</v>
+        <v>0.001194881462916408</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.002356495561037886</v>
+        <v>0.001970226527072527</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.000795385311694341</v>
+        <v>0.0001952679826716319</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.003118377953231399</v>
+        <v>0.005102957188573959</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0.002457237618868613</v>
+        <v>-0.002792234444727692</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.0042798360323282</v>
+        <v>-0.001553932762923527</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.0004725406345422345</v>
+        <v>0.000312269215025618</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.653648072890146e-05</v>
+        <v>-0.0001332425922882963</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.0002245745353835538</v>
+        <v>8.923259964306318e-05</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-0.003148184481180078</v>
+        <v>-0.0006510277441299283</v>
       </c>
       <c r="AK7" t="n">
-        <v>-0.0003518234822671386</v>
+        <v>-0.003532448662409082</v>
       </c>
       <c r="AL7" t="n">
-        <v>-0.0003395711081269015</v>
+        <v>-0.0002702659666097895</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.0002272293356147648</v>
+        <v>-0.0004316310583457661</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.0009220184249878471</v>
+        <v>0.0001088862783927669</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.003326489178706077</v>
+        <v>-0.002923816394441198</v>
       </c>
       <c r="AP7" t="n">
-        <v>-0.000648488011330367</v>
+        <v>-4.321521175458254e-05</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.001621408676353864</v>
+        <v>0.0006747721484392899</v>
       </c>
       <c r="AR7" t="n">
-        <v>-0.003524759564163748</v>
+        <v>-0.0008119359585593677</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.0007048734636458609</v>
+        <v>0.001462594898061975</v>
       </c>
       <c r="AT7" t="n">
-        <v>-0.003129530309587708</v>
+        <v>-0.002750304761481526</v>
       </c>
       <c r="AU7" t="n">
-        <v>-0.001415587690290115</v>
+        <v>0.001469150016843534</v>
       </c>
       <c r="AV7" t="n">
-        <v>-0.0006948267442166867</v>
+        <v>0.0003022024184525573</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.0008479278502302679</v>
+        <v>0.0005230433428339898</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.0003940021707219521</v>
+        <v>-0.0001460336418526165</v>
       </c>
       <c r="AY7" t="n">
-        <v>-0.000437427003079105</v>
+        <v>0.003423531045124184</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.004620367795502234</v>
+        <v>4.267143394659501e-05</v>
       </c>
       <c r="BA7" t="n">
-        <v>-0.002552314705025049</v>
+        <v>-0.00045837462509557</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.001251990841227496</v>
+        <v>-0.00284985383417502</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.0001775410990552007</v>
+        <v>-0.0001314755260617029</v>
       </c>
       <c r="BD7" t="n">
-        <v>-5.974277363303693e-05</v>
+        <v>7.38552437223039e-05</v>
       </c>
       <c r="BE7" t="n">
-        <v>2.974419988103771e-05</v>
+        <v>-7.368110816387552e-05</v>
       </c>
       <c r="BF7" t="n">
-        <v>-0.004745844539671873</v>
+        <v>-0.001572657401708921</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.001157799994231073</v>
+        <v>0.001294073410199137</v>
       </c>
       <c r="BH7" t="n">
         <v>0</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.0001770696347573986</v>
+        <v>0.0002193669696019973</v>
       </c>
       <c r="BJ7" t="n">
-        <v>8.444977680745485e-05</v>
+        <v>0.001016683272156526</v>
       </c>
       <c r="BK7" t="n">
-        <v>-0.002304095753186353</v>
+        <v>0.0001716036758949769</v>
       </c>
       <c r="BL7" t="n">
-        <v>-0.0001474752657895873</v>
+        <v>0.0005711535307378002</v>
       </c>
       <c r="BM7" t="n">
-        <v>-0.001797729458023806</v>
+        <v>-0.0001131706526262377</v>
       </c>
       <c r="BN7" t="n">
-        <v>-0.001620417838760885</v>
+        <v>-0.004573103368399983</v>
       </c>
       <c r="BO7" t="n">
-        <v>-0.0004278728606356696</v>
+        <v>0.001953469832298144</v>
       </c>
       <c r="BP7" t="n">
-        <v>-0.0007812145121668723</v>
+        <v>0.001398078445604145</v>
       </c>
       <c r="BQ7" t="n">
-        <v>-0.0001201043463965601</v>
+        <v>6.088023600348546e-05</v>
       </c>
       <c r="BR7" t="n">
-        <v>0.0001176383985821705</v>
+        <v>-0.0005410058193737355</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.0003243189872573882</v>
+        <v>-0.0002601806132184138</v>
       </c>
       <c r="BT7" t="n">
-        <v>-0.000367132204956111</v>
+        <v>-0.0005928487805702765</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.00159981103904106</v>
+        <v>-0.0004124310387130126</v>
       </c>
       <c r="BV7" t="n">
-        <v>-0.0003420582986317533</v>
+        <v>0.0005729741189562321</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.000866065548483369</v>
+        <v>-0.001595828533043448</v>
       </c>
       <c r="BX7" t="n">
-        <v>4.429148379570535e-05</v>
+        <v>3.056234718825101e-05</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.0001343547994793137</v>
+        <v>-0.00029633043565368</v>
       </c>
       <c r="BZ7" t="n">
-        <v>-0.0008924784416930287</v>
+        <v>0.0004060024802030437</v>
       </c>
       <c r="CA7" t="n">
         <v>0</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.000319244230443344</v>
+        <v>-0.0003394988994675884</v>
       </c>
       <c r="CC7" t="n">
-        <v>-2.769626056949308e-05</v>
+        <v>0.001025121591418154</v>
       </c>
       <c r="CD7" t="n">
         <v>0</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.0003298951672598971</v>
+        <v>-0.000546650654136116</v>
       </c>
       <c r="CF7" t="n">
-        <v>0.00127561025631569</v>
+        <v>-0.0006706655267688043</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.000534385085897926</v>
+        <v>0.0004011476958530547</v>
       </c>
       <c r="CH7" t="n">
-        <v>-0.0001933952911050807</v>
+        <v>-6.208372599346146e-05</v>
       </c>
       <c r="CI7" t="n">
-        <v>-0.0009000679612931107</v>
+        <v>-0.0003779483410559281</v>
       </c>
       <c r="CJ7" t="n">
-        <v>-0.0006055438700210802</v>
+        <v>-0.0005500589171121839</v>
       </c>
       <c r="CK7" t="n">
-        <v>-0.0006491420725728558</v>
+        <v>-0.0008071726333243768</v>
       </c>
     </row>
     <row r="8">
@@ -2503,268 +2503,268 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0001495072103664924</v>
+        <v>0.002277686574279075</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001817064471986577</v>
+        <v>0.001444555566565303</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002847087443017671</v>
+        <v>0.001052035065091128</v>
       </c>
       <c r="F8" t="n">
-        <v>0.002729143648504517</v>
+        <v>0.004225672475174897</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0006559866530554681</v>
+        <v>0.0006219144218163664</v>
       </c>
       <c r="H8" t="n">
-        <v>0.004247880260037968</v>
+        <v>0.001734764494281021</v>
       </c>
       <c r="I8" t="n">
-        <v>7.37881584928185e-05</v>
+        <v>0.0002155052228676762</v>
       </c>
       <c r="J8" t="n">
-        <v>0.002925644741374428</v>
+        <v>0.002793125580705805</v>
       </c>
       <c r="K8" t="n">
-        <v>0.02730763367096149</v>
+        <v>0.02573296810089439</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02230161673126622</v>
+        <v>0.02757391731610346</v>
       </c>
       <c r="M8" t="n">
-        <v>0.001260609251698003</v>
+        <v>0.0006661830934214241</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0005533070817180963</v>
+        <v>0.003618894003060324</v>
       </c>
       <c r="O8" t="n">
-        <v>0.008409040745917654</v>
+        <v>0.009693295664619244</v>
       </c>
       <c r="P8" t="n">
-        <v>0.01079470197777005</v>
+        <v>0.01416844639088512</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0126038463201077</v>
+        <v>0.01444578211001299</v>
       </c>
       <c r="R8" t="n">
-        <v>0.002277226968297216</v>
+        <v>0.001309413596501613</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0004770134945548649</v>
+        <v>-5.226367625632832e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>0.002329298265903745</v>
+        <v>0.002035944390071279</v>
       </c>
       <c r="U8" t="n">
-        <v>0.001279718746409281</v>
+        <v>0.0007989111116078279</v>
       </c>
       <c r="V8" t="n">
-        <v>-3.910422791089385e-05</v>
+        <v>0.0003858478833725421</v>
       </c>
       <c r="W8" t="n">
-        <v>0.003656101300231743</v>
+        <v>0.004722337248237624</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.001105820441455993</v>
+        <v>0.001993503526364629</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.003085569399787446</v>
+        <v>0.00265185655582239</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.003501603257108313</v>
+        <v>0.002526425493861148</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.003979952301540327</v>
+        <v>0.004532978912307137</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.0009478701575189707</v>
+        <v>0.0006634794127397092</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.007818223073750507</v>
+        <v>0.008173732090255948</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.0007169974140540797</v>
+        <v>0.0029685825938848</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.001989774797242297</v>
+        <v>-0.000547596772153483</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.0008617408442599839</v>
+        <v>0.002784042194818081</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.0006609722670743723</v>
+        <v>3.847540996602949e-05</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.0007663574015682462</v>
+        <v>0.0005754565884233537</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>-0.0004441427869478987</v>
+        <v>0.001226842581859927</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.005182363759962988</v>
+        <v>-0.0002206502850372605</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.0002284810895313572</v>
+        <v>-2.607411669630362e-08</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.0006023992365435409</v>
+        <v>0.0003960735966143325</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.00181073393006754</v>
+        <v>0.003535529378060301</v>
       </c>
       <c r="AO8" t="n">
-        <v>-0.0002030470011080476</v>
+        <v>0.0002080954234745247</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.0002569634564095175</v>
+        <v>0.0003421980642396128</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.00292644876526765</v>
+        <v>0.001782464867560285</v>
       </c>
       <c r="AR8" t="n">
-        <v>-0.001120483733321478</v>
+        <v>0.0008484197703464091</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.002531119587455238</v>
+        <v>0.002207879627047527</v>
       </c>
       <c r="AT8" t="n">
-        <v>-0.0003181677448791581</v>
+        <v>0.0007326886311177783</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.002250235864412761</v>
+        <v>0.004418372381992863</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.001720386749730052</v>
+        <v>0.002272625324539193</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.00240679127360788</v>
+        <v>0.004738011593647634</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.0006067299839446399</v>
+        <v>0.0003036113680755514</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.0006461891217970832</v>
+        <v>0.004171599691796884</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.007287051604866018</v>
+        <v>0.004198246169455552</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.002093822395848377</v>
+        <v>0.001539902442548396</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.004258685264109513</v>
+        <v>0.002701795903548054</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.0004836814162221398</v>
+        <v>0.000289946226492091</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.0003095651356232909</v>
+        <v>0.0002087599662165207</v>
       </c>
       <c r="BE8" t="n">
-        <v>8.876403315224712e-05</v>
+        <v>0.0003181788732907587</v>
       </c>
       <c r="BF8" t="n">
-        <v>-0.0005673220141856699</v>
+        <v>0.001340928612554146</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.0009059262270162405</v>
+        <v>0.006282207473983059</v>
       </c>
       <c r="BH8" t="n">
         <v>0</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.0006817692023084493</v>
+        <v>0.0008060687058665695</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.0009375784970446944</v>
+        <v>0.003164864260744682</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.0007481172830541337</v>
+        <v>0.001833130307935341</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.0004389844817980049</v>
+        <v>0.0007184395551187827</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.002265778817968858</v>
+        <v>0.00129888846955323</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.0008406477598365768</v>
+        <v>0.0002062845575727806</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.002313690152429135</v>
+        <v>0.003839177432135521</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.001277563746227964</v>
+        <v>0.004654223738987859</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.531684385503388e-05</v>
+        <v>0.0002006676859646256</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.002389006447510886</v>
+        <v>0.001897001437504875</v>
       </c>
       <c r="BS8" t="n">
-        <v>0.002854162072521926</v>
+        <v>0.002739705270152948</v>
       </c>
       <c r="BT8" t="n">
-        <v>0.0004357328236833296</v>
+        <v>-0.0001229616461079663</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.008188873247148554</v>
+        <v>0.005950149124488971</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.002475689756694902</v>
+        <v>0.001198486430969262</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.002753977087371159</v>
+        <v>0.001345670670745297</v>
       </c>
       <c r="BX8" t="n">
-        <v>6.167397201536917e-05</v>
+        <v>0.0002238418673651571</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.000537850039780166</v>
+        <v>1.303349096508366e-05</v>
       </c>
       <c r="BZ8" t="n">
-        <v>-0.0001183199667497442</v>
+        <v>0.0007148023542841719</v>
       </c>
       <c r="CA8" t="n">
-        <v>2.219591595146453e-05</v>
+        <v>0</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.0005755901209804238</v>
+        <v>0.0004684711481261094</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.001717084853966416</v>
+        <v>0.002192873480805677</v>
       </c>
       <c r="CD8" t="n">
         <v>0</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.0007357204300745462</v>
+        <v>-0.0003307700993416457</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.003301178732594534</v>
+        <v>8.538291159828071e-05</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.002532732096662182</v>
+        <v>0.003659778128344893</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.0006585054217357611</v>
+        <v>0.0003771369163825256</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.0004451233391152303</v>
+        <v>0.002244826630662602</v>
       </c>
       <c r="CJ8" t="n">
-        <v>0.002891560422630004</v>
+        <v>0.009162017834760271</v>
       </c>
       <c r="CK8" t="n">
-        <v>0.0007077049723823281</v>
+        <v>0.001561174846573843</v>
       </c>
     </row>
     <row r="9">
@@ -2774,268 +2774,268 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.003538779121203195</v>
+        <v>0.005335413416536627</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01114058355437664</v>
+        <v>0.003949307397583313</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0156498673740053</v>
+        <v>0.01470674918950785</v>
       </c>
       <c r="F9" t="n">
-        <v>0.004069595989383668</v>
+        <v>0.006246281975014867</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01087533156498672</v>
+        <v>0.01825273010920432</v>
       </c>
       <c r="H9" t="n">
-        <v>0.008846947803007954</v>
+        <v>0.00851794071762868</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0006864274570982154</v>
+        <v>0.000589796520200514</v>
       </c>
       <c r="J9" t="n">
-        <v>0.007810197465369861</v>
+        <v>0.01900156006240246</v>
       </c>
       <c r="K9" t="n">
-        <v>0.04061302681992336</v>
+        <v>0.04099616858237554</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04665487768936044</v>
+        <v>0.04768641320365465</v>
       </c>
       <c r="M9" t="n">
-        <v>0.002929860905593318</v>
+        <v>0.01010920436817467</v>
       </c>
       <c r="N9" t="n">
-        <v>0.01052166224580018</v>
+        <v>0.007793398533007334</v>
       </c>
       <c r="O9" t="n">
-        <v>0.01296787503684055</v>
+        <v>0.01781591263650544</v>
       </c>
       <c r="P9" t="n">
-        <v>0.01927424152290304</v>
+        <v>0.02152886115444614</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.02748364069006545</v>
+        <v>0.02758620689655178</v>
       </c>
       <c r="R9" t="n">
-        <v>0.006867079280872368</v>
+        <v>0.006521060842433646</v>
       </c>
       <c r="S9" t="n">
-        <v>0.009048040082522824</v>
+        <v>0.004523227383863115</v>
       </c>
       <c r="T9" t="n">
-        <v>0.005502676977989307</v>
+        <v>0.003716508210890201</v>
       </c>
       <c r="U9" t="n">
-        <v>0.008635425876805181</v>
+        <v>0.004244031830238781</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0001474491300501368</v>
+        <v>0.0005918910920390541</v>
       </c>
       <c r="W9" t="n">
-        <v>0.01247419640224124</v>
+        <v>0.01959046454767727</v>
       </c>
       <c r="X9" t="n">
-        <v>0.005013270421704507</v>
+        <v>0.008153269951022713</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.007075192421551224</v>
+        <v>0.006115444617784671</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.005334512231063937</v>
+        <v>0.006677067082683253</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.007674003569304</v>
+        <v>0.01092043681747266</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.001267315060418495</v>
+        <v>0.001347539956126609</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.01885782272456874</v>
+        <v>0.01638905413444378</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.01154074955383703</v>
+        <v>0.008506841165972634</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.003428406799193351</v>
+        <v>0.001834862385321123</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.002481536189069411</v>
+        <v>0.006770383174877537</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.0009136457412319387</v>
+        <v>0.001008354940939182</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.001963117192147579</v>
+        <v>0.0007778738115816419</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.003072378138847842</v>
+        <v>0.006338231057332144</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.007762836185819089</v>
+        <v>0.004519940915804999</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.001124593074874203</v>
+        <v>0.002028081123244874</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.003123140987507467</v>
+        <v>0.001361349511689858</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.007584770969660937</v>
+        <v>0.01157566302652103</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.00458081244598102</v>
+        <v>0.002794583693460062</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.0009136457412319277</v>
+        <v>0.00124804992199683</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.004091040046096261</v>
+        <v>0.003183023872679081</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.007058484586574498</v>
+        <v>0.005445116681071704</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.008536585365853677</v>
+        <v>0.00730109204368169</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.001710409908581534</v>
+        <v>0.003993759750389969</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.006837606837606813</v>
+        <v>0.01797819039198355</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.003866745984533038</v>
+        <v>0.006302652106084194</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.00400366748166262</v>
+        <v>0.01063955201886242</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.000951814396192785</v>
+        <v>0.0006240249609983928</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.002071618822136689</v>
+        <v>0.007987032124963222</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.01674034777483052</v>
+        <v>0.01252230814991077</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.007810197465369861</v>
+        <v>0.002995319812792463</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.01049837805956946</v>
+        <v>0.004232021308079347</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.0007640586797066362</v>
+        <v>0.001827291482463944</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.001591263650545971</v>
+        <v>0.002740937223695894</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.003225806451612845</v>
+        <v>0.000531757754800588</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.007976366322008831</v>
+        <v>0.003308714918759214</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.009637488947833761</v>
+        <v>0.0098143236074271</v>
       </c>
       <c r="BH9" t="n">
         <v>0</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.001296787503684049</v>
+        <v>0.00327613104524177</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.002171326591314737</v>
+        <v>0.005658709106985005</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.006045414332055454</v>
+        <v>0.0049335302806499</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.002340093603744109</v>
+        <v>0.001444149720011823</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.003279172821270293</v>
+        <v>0.003777513384889963</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.006039076376554198</v>
+        <v>0.00445033893309762</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.004420866489832009</v>
+        <v>0.005589167386920146</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.006335109532267602</v>
+        <v>0.01201382886776144</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.0003120124804991686</v>
+        <v>0.0005473926822240904</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.008728988498967871</v>
+        <v>0.01082683307332289</v>
       </c>
       <c r="BS9" t="n">
-        <v>0.003716508210890268</v>
+        <v>0.005305039787798449</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.002808112324492928</v>
+        <v>0.001560062402496043</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.03282217634915955</v>
+        <v>0.02094497263036586</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.006394316163410308</v>
+        <v>0.002239905688181587</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.01179593040401061</v>
+        <v>0.01264765197349465</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.0001178897730621853</v>
+        <v>0.0004135893648449018</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.00287152161042038</v>
+        <v>0.0007202535292422541</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.001386021822471251</v>
+        <v>0.005877268798617085</v>
       </c>
       <c r="CA9" t="n">
-        <v>0.0001560062402495843</v>
+        <v>0</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.001219512195121974</v>
+        <v>0.004033419763756807</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.007195517546446473</v>
+        <v>0.0075770671276289</v>
       </c>
       <c r="CD9" t="n">
-        <v>5.918910920390541e-05</v>
+        <v>0.0002676977989291895</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.00168486739469571</v>
+        <v>0.001213735938425087</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.004955344281186991</v>
+        <v>0.004609622587150653</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.00455756140870075</v>
+        <v>0.007581903276130997</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.00202260559190961</v>
+        <v>0.002122015915119413</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.001621940430551472</v>
+        <v>0.01983495431771298</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.003597758773223236</v>
+        <v>0.01435307987032128</v>
       </c>
       <c r="CK9" t="n">
-        <v>0.004550862581796577</v>
+        <v>0.002736466389054126</v>
       </c>
     </row>
   </sheetData>
